--- a/latest.xlsx
+++ b/latest.xlsx
@@ -565,13 +565,13 @@
         <v>-0.0001</v>
       </c>
       <c r="N2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="O2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="P2" s="1">
-        <v>-4.81</v>
+        <v>-5.01</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864.4</v>
+        <v>865.6</v>
       </c>
       <c r="D3" s="1">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0019</v>
+        <v>0.0032</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="L3" s="1">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="O3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="P3" s="1">
-        <v>-5.02</v>
+        <v>-4.22</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0084</v>
+        <v>0.0098</v>
       </c>
       <c r="U3" s="5">
-        <v>2.161</v>
+        <v>2.164</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0379</v>
+        <v>0.0394</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0942</v>
+        <v>0.0957</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0936</v>
+        <v>0.0951</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.129</v>
+        <v>0.1306</v>
       </c>
     </row>
     <row r="4">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>992</v>
+        <v>993.2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,16 +802,16 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0007</v>
+        <v>0.0019</v>
       </c>
       <c r="L5" s="1">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0007</v>
+        <v>0.0019</v>
       </c>
       <c r="N5" s="1">
         <v>-2.42</v>
@@ -832,10 +832,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0151</v>
+        <v>0.0164</v>
       </c>
       <c r="U5" s="5">
-        <v>4.96</v>
+        <v>4.966</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0685</v>
+        <v>0.0698</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0479</v>
+        <v>0.0492</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0586</v>
+        <v>0.0599</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3191</v>
+        <v>0.3207</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>976.8</v>
+        <v>977.4</v>
       </c>
       <c r="D6" s="1">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0033</v>
+        <v>0.0039</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0032</v>
+        <v>0.0038</v>
       </c>
       <c r="L6" s="1">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0032</v>
+        <v>0.0038</v>
       </c>
       <c r="N6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="O6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="P6" s="1">
-        <v>-3.12</v>
+        <v>-3.02</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0326</v>
@@ -915,10 +915,10 @@
         <v>1</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0113</v>
+        <v>-0.0107</v>
       </c>
       <c r="U6" s="5">
-        <v>9.768</v>
+        <v>9.774</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0204</v>
+        <v>-0.0198</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0845</v>
+        <v>-0.0839</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0931</v>
+        <v>0.0937</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.297</v>
+        <v>0.2978</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-5.06</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1008</v>
+        <v>0.1007</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>787.2</v>
+        <v>789.4</v>
       </c>
       <c r="D8" s="1">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0008</v>
+        <v>0.0036</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,16 +1051,16 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0006</v>
+        <v>0.0034</v>
       </c>
       <c r="L8" s="1">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0006</v>
+        <v>0.0034</v>
       </c>
       <c r="N8" s="1">
         <v>-4.62</v>
@@ -1081,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0342</v>
+        <v>0.037</v>
       </c>
       <c r="U8" s="5">
-        <v>3.936</v>
+        <v>3.947</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1452</v>
+        <v>0.1484</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1888</v>
+        <v>0.1921</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2464</v>
+        <v>0.2498</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9838</v>
+        <v>0.9894</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20326.6</v>
+        <v>20347.6</v>
       </c>
       <c r="D9" s="1">
-        <v>-49</v>
+        <v>-28</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0024</v>
+        <v>-0.0014</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-51.04</v>
+        <v>-30.04</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0025</v>
+        <v>-0.0015</v>
       </c>
       <c r="L9" s="1">
-        <v>-51.04</v>
+        <v>-30.04</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0025</v>
+        <v>-0.0015</v>
       </c>
       <c r="N9" s="1">
         <v>-30.61</v>
@@ -1155,7 +1155,7 @@
         <v>-30.61</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6788</v>
+        <v>0.6789</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>1</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0022</v>
+        <v>0.0032</v>
       </c>
       <c r="U9" s="5">
-        <v>14.519</v>
+        <v>14.534</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0025</v>
+        <v>0.0014</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0386</v>
+        <v>0.0397</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0047</v>
+        <v>-0.0037</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0618</v>
+        <v>0.0629</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2157</v>
+        <v>0.2169</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>665.6</v>
+        <v>665.2</v>
       </c>
       <c r="D10" s="1">
-        <v>-6.4</v>
+        <v>-6.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0095</v>
+        <v>-0.0101</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0103</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0103</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.81</v>
+        <v>-5.41</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0222</v>
@@ -1247,28 +1247,28 @@
         <v>1</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="U10" s="5">
-        <v>1.664</v>
+        <v>1.663</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0096</v>
+        <v>0.0102</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0303</v>
+        <v>0.0297</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.293</v>
+        <v>0.2922</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3517</v>
+        <v>0.3509</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.303</v>
+        <v>0.3022</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="O11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="P11" s="1">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0287</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29938.8</v>
+        <v>29964.6</v>
       </c>
       <c r="D12" s="1">
-        <v>-50</v>
+        <v>-24.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0017</v>
+        <v>-0.0008</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-52.99</v>
+        <v>-27.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0018</v>
+        <v>-0.0009</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="P12" s="1">
-        <v>-72.6</v>
+        <v>-71.9</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -648,13 +648,13 @@
         <v>0.0031</v>
       </c>
       <c r="N3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="O3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="P3" s="1">
-        <v>-4.22</v>
+        <v>-2.22</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -731,13 +731,13 @@
         <v>-0.0001</v>
       </c>
       <c r="N4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="O4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="P4" s="1">
-        <v>-6.11</v>
+        <v>-5.01</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0246</v>
@@ -814,13 +814,13 @@
         <v>0.0019</v>
       </c>
       <c r="N5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="O5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="P5" s="1">
-        <v>-2.42</v>
+        <v>-3.02</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0331</v>
@@ -897,13 +897,13 @@
         <v>0.0038</v>
       </c>
       <c r="N6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="O6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="P6" s="1">
-        <v>-3.02</v>
+        <v>-1.22</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0326</v>
@@ -1063,13 +1063,13 @@
         <v>0.0034</v>
       </c>
       <c r="N8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="O8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="P8" s="1">
-        <v>-4.62</v>
+        <v>-2.22</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0263</v>
@@ -1146,13 +1146,13 @@
         <v>-0.0015</v>
       </c>
       <c r="N9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="O9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="P9" s="1">
-        <v>-30.61</v>
+        <v>-33.41</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6789</v>
@@ -1229,13 +1229,13 @@
         <v>-0.0103</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.41</v>
+        <v>-11.81</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0222</v>
@@ -1312,13 +1312,13 @@
         <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="O11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="P11" s="1">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0287</v>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="P12" s="1">
-        <v>-71.9</v>
+        <v>-74.8</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1499,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1538,34 +1538,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B2" t="str">
-        <v>14:02:01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>510300</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>300ETF</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4.956</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-991.2</v>
-      </c>
-      <c r="I2" s="6">
-        <v>991.2</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1576,13 +1570,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B3" t="str">
-        <v>14:02:37</v>
+        <v>14:02:01</v>
       </c>
       <c r="C3" t="str">
-        <v>512100</v>
+        <v>510300</v>
       </c>
       <c r="D3" t="str">
-        <v>1000ETF</v>
+        <v>300ETF</v>
       </c>
       <c r="E3" t="str">
         <v>买入</v>
@@ -1591,13 +1585,13 @@
         <v>200</v>
       </c>
       <c r="G3">
-        <v>3.555</v>
+        <v>4.956</v>
       </c>
       <c r="H3">
-        <v>-711</v>
+        <v>-991.2</v>
       </c>
       <c r="I3" s="6">
-        <v>711</v>
+        <v>991.2</v>
       </c>
       <c r="J3" s="6">
         <v>0</v>
@@ -1611,13 +1605,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B4" t="str">
-        <v>14:02:50</v>
+        <v>14:02:37</v>
       </c>
       <c r="C4" t="str">
-        <v>159915</v>
+        <v>512100</v>
       </c>
       <c r="D4" t="str">
-        <v>创业板</v>
+        <v>1000ETF</v>
       </c>
       <c r="E4" t="str">
         <v>买入</v>
@@ -1626,13 +1620,13 @@
         <v>200</v>
       </c>
       <c r="G4">
-        <v>3.933</v>
+        <v>3.555</v>
       </c>
       <c r="H4">
-        <v>-786.6</v>
+        <v>-711</v>
       </c>
       <c r="I4" s="6">
-        <v>786.6</v>
+        <v>711</v>
       </c>
       <c r="J4" s="6">
         <v>0</v>
@@ -1646,28 +1640,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B5" t="str">
-        <v>14:03:06</v>
+        <v>14:02:50</v>
       </c>
       <c r="C5" t="str">
-        <v>513010</v>
+        <v>159915</v>
       </c>
       <c r="D5" t="str">
-        <v>港股科技</v>
+        <v>创业板</v>
       </c>
       <c r="E5" t="str">
         <v>买入</v>
       </c>
       <c r="F5">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>0.67</v>
+        <v>3.933</v>
       </c>
       <c r="H5">
-        <v>-737</v>
+        <v>-786.6</v>
       </c>
       <c r="I5" s="6">
-        <v>737</v>
+        <v>786.6</v>
       </c>
       <c r="J5" s="6">
         <v>0</v>
@@ -1681,28 +1675,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B6" t="str">
-        <v>14:03:51</v>
+        <v>14:03:06</v>
       </c>
       <c r="C6" t="str">
-        <v>518880</v>
+        <v>513010</v>
       </c>
       <c r="D6" t="str">
-        <v>黄金ETF</v>
+        <v>港股科技</v>
       </c>
       <c r="E6" t="str">
         <v>买入</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="G6">
-        <v>9.736</v>
+        <v>0.67</v>
       </c>
       <c r="H6">
-        <v>-973.6</v>
+        <v>-737</v>
       </c>
       <c r="I6" s="6">
-        <v>973.6</v>
+        <v>737</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
@@ -1716,28 +1710,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B7" t="str">
-        <v>14:04:05</v>
+        <v>14:03:51</v>
       </c>
       <c r="C7" t="str">
-        <v>159981</v>
+        <v>518880</v>
       </c>
       <c r="D7" t="str">
-        <v>能源化工</v>
+        <v>黄金ETF</v>
       </c>
       <c r="E7" t="str">
         <v>买入</v>
       </c>
       <c r="F7">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>9.736</v>
       </c>
       <c r="H7">
-        <v>-672</v>
+        <v>-973.6</v>
       </c>
       <c r="I7" s="6">
-        <v>672</v>
+        <v>973.6</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
@@ -1751,13 +1745,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B8" t="str">
-        <v>14:04:16</v>
+        <v>14:04:05</v>
       </c>
       <c r="C8" t="str">
-        <v>159985</v>
+        <v>159981</v>
       </c>
       <c r="D8" t="str">
-        <v>豆粕ETF</v>
+        <v>能源化工</v>
       </c>
       <c r="E8" t="str">
         <v>买入</v>
@@ -1766,13 +1760,13 @@
         <v>400</v>
       </c>
       <c r="G8">
-        <v>2.157</v>
+        <v>1.68</v>
       </c>
       <c r="H8">
-        <v>-862.8</v>
+        <v>-672</v>
       </c>
       <c r="I8" s="6">
-        <v>862.8</v>
+        <v>672</v>
       </c>
       <c r="J8" s="6">
         <v>0</v>
@@ -1786,28 +1780,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B9" t="str">
-        <v>14:04:34</v>
+        <v>14:04:16</v>
       </c>
       <c r="C9" t="str">
-        <v>511380</v>
+        <v>159985</v>
       </c>
       <c r="D9" t="str">
-        <v>转债ETF</v>
+        <v>豆粕ETF</v>
       </c>
       <c r="E9" t="str">
         <v>买入</v>
       </c>
       <c r="F9">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="G9">
-        <v>14.554</v>
+        <v>2.157</v>
       </c>
       <c r="H9">
-        <v>-20375.6</v>
+        <v>-862.8</v>
       </c>
       <c r="I9" s="6">
-        <v>20375.6</v>
+        <v>862.8</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
@@ -1821,28 +1815,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B10" t="str">
-        <v>14:04:49</v>
+        <v>14:04:34</v>
       </c>
       <c r="C10" t="str">
-        <v>166016</v>
+        <v>511380</v>
       </c>
       <c r="D10" t="str">
-        <v>中欧纯债</v>
+        <v>转债ETF</v>
       </c>
       <c r="E10" t="str">
         <v>买入</v>
       </c>
       <c r="F10">
-        <v>2700</v>
+        <v>1400</v>
       </c>
       <c r="G10">
-        <v>1.118</v>
+        <v>14.554</v>
       </c>
       <c r="H10">
-        <v>-3018.6</v>
+        <v>-20375.6</v>
       </c>
       <c r="I10" s="6">
-        <v>3018.6</v>
+        <v>20375.6</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -1856,40 +1850,75 @@
         <v>2026-05-11</v>
       </c>
       <c r="B11" t="str">
-        <v>14:05:33</v>
+        <v>14:04:49</v>
       </c>
       <c r="C11" t="str">
-        <v>159980</v>
+        <v>166016</v>
       </c>
       <c r="D11" t="str">
-        <v>有色ETF</v>
+        <v>中欧纯债</v>
       </c>
       <c r="E11" t="str">
         <v>买入</v>
       </c>
       <c r="F11">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="G11">
-        <v>2.151</v>
+        <v>1.118</v>
       </c>
       <c r="H11">
-        <v>-860.4</v>
+        <v>-3018.6</v>
       </c>
       <c r="I11" s="6">
-        <v>860.4</v>
+        <v>3018.6</v>
       </c>
       <c r="J11" s="6">
         <v>0</v>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>14:05:33</v>
+      </c>
+      <c r="C12" t="str">
+        <v>159980</v>
+      </c>
+      <c r="D12" t="str">
+        <v>有色ETF</v>
+      </c>
+      <c r="E12" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F12">
+        <v>400</v>
+      </c>
+      <c r="G12">
+        <v>2.151</v>
+      </c>
+      <c r="H12">
+        <v>-860.4</v>
+      </c>
+      <c r="I12" s="6">
+        <v>860.4</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>710</v>
+        <v>709.2</v>
       </c>
       <c r="D2" s="1">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0014</v>
+        <v>-0.0025</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0015</v>
+        <v>-0.0027</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0015</v>
+        <v>-0.0027</v>
       </c>
       <c r="N2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="O2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="P2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0014</v>
+        <v>-0.0025</v>
       </c>
       <c r="U2" s="5">
-        <v>3.55</v>
+        <v>3.546</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0017</v>
+        <v>0.0028</v>
       </c>
       <c r="X2" s="2">
-        <v>0.109</v>
+        <v>0.1078</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0748</v>
+        <v>0.0736</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1776</v>
+        <v>0.1763</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4748</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>867.6</v>
+        <v>866</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0023</v>
+        <v>0.0005</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0054</v>
+        <v>0.0036</v>
       </c>
       <c r="L3" s="1">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0054</v>
+        <v>0.0036</v>
       </c>
       <c r="N3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="2">
         <v>0.029</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0023</v>
+        <v>0.0005</v>
       </c>
       <c r="U3" s="5">
-        <v>2.169</v>
+        <v>2.165</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0418</v>
+        <v>0.0399</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0916</v>
+        <v>0.0896</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0999</v>
+        <v>0.0979</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1332</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>740.3</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.0028</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.0028</v>
+      </c>
+      <c r="N4" s="1">
         <v>3.2</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.0043</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="O4" s="1">
         <v>3.2</v>
       </c>
-      <c r="M4" s="2">
-        <v>0.0043</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>2.1</v>
-      </c>
       <c r="P4" s="1">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.673</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0483</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0843</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1762</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0665</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994.2</v>
+        <v>994</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="L5" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="N5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="P5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="U5" s="5">
-        <v>4.971</v>
+        <v>4.97</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0708</v>
+        <v>0.0706</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.322</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.9</v>
+        <v>985.8</v>
       </c>
       <c r="D6" s="1">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0097</v>
+        <v>0.0086</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0136</v>
+        <v>0.0124</v>
       </c>
       <c r="L6" s="1">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0136</v>
+        <v>0.0124</v>
       </c>
       <c r="N6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="P6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0097</v>
+        <v>0.0086</v>
       </c>
       <c r="U6" s="5">
-        <v>9.869</v>
+        <v>9.858</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0104</v>
+        <v>-0.0115</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0827</v>
+        <v>-0.0837</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0891</v>
+        <v>0.0879</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3104</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1009</v>
+        <v>0.101</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.2</v>
+        <v>790.8</v>
       </c>
       <c r="D8" s="1">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0044</v>
+        <v>0.0052</v>
       </c>
       <c r="L8" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0044</v>
+        <v>0.0052</v>
       </c>
       <c r="N8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="O8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="P8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
       <c r="U8" s="5">
-        <v>3.951</v>
+        <v>3.954</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1496</v>
+        <v>0.1504</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2071</v>
+        <v>0.208</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2692</v>
+        <v>0.2701</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9914</v>
+        <v>0.9929</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20262.2</v>
+        <v>20246.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-85.4</v>
+        <v>-100.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0042</v>
+        <v>-0.005</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-115.44</v>
+        <v>-130.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0057</v>
+        <v>-0.0064</v>
       </c>
       <c r="L9" s="1">
-        <v>-115.44</v>
+        <v>-130.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0057</v>
+        <v>-0.0064</v>
       </c>
       <c r="N9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6772</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0042</v>
+        <v>-0.005</v>
       </c>
       <c r="U9" s="5">
-        <v>14.473</v>
+        <v>14.462</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0057</v>
+        <v>0.0064</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0352</v>
+        <v>0.0344</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.009</v>
+        <v>-0.0097</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0607</v>
+        <v>0.0599</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2118</v>
+        <v>0.2109</v>
       </c>
     </row>
     <row r="10">
@@ -1229,16 +1229,16 @@
         <v>-0.0097</v>
       </c>
       <c r="N10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0222</v>
+        <v>0.0223</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>876.4</v>
+        <v>874.8</v>
       </c>
       <c r="D11" s="1">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0195</v>
+        <v>0.0177</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0185</v>
+        <v>0.0166</v>
       </c>
       <c r="L11" s="1">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0185</v>
+        <v>0.0166</v>
       </c>
       <c r="N11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="O11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="P11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0293</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0195</v>
+        <v>0.0177</v>
       </c>
       <c r="U11" s="5">
-        <v>2.191</v>
+        <v>2.187</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.073</v>
+        <v>0.071</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0398</v>
+        <v>0.0379</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2092</v>
+        <v>0.207</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3247</v>
+        <v>0.3223</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29912</v>
+        <v>29890.8</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.6</v>
+        <v>-73.8</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0018</v>
+        <v>-0.0025</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-79.79</v>
+        <v>-100.99</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0027</v>
+        <v>-0.0034</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="O12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="P12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>709.2</v>
+        <v>708.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0025</v>
+        <v>-0.0034</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
+        <v>-2.5</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-0.0035</v>
+      </c>
+      <c r="L2" s="1">
+        <v>-2.5</v>
+      </c>
+      <c r="M2" s="2">
+        <v>-0.0035</v>
+      </c>
+      <c r="N2" s="1">
         <v>-1.9</v>
       </c>
-      <c r="K2" s="2">
-        <v>-0.0027</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="O2" s="1">
         <v>-1.9</v>
       </c>
-      <c r="M2" s="2">
-        <v>-0.0027</v>
-      </c>
-      <c r="N2" s="1">
-        <v>-1.7</v>
-      </c>
-      <c r="O2" s="1">
-        <v>-1.7</v>
-      </c>
       <c r="P2" s="1">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0025</v>
+        <v>-0.0034</v>
       </c>
       <c r="U2" s="5">
-        <v>3.546</v>
+        <v>3.543</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0028</v>
+        <v>0.0037</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1078</v>
+        <v>0.1069</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0736</v>
+        <v>0.0727</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1763</v>
+        <v>0.1753</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4732</v>
+        <v>0.4719</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866</v>
+        <v>866.4</v>
       </c>
       <c r="D3" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0036</v>
+        <v>0.0041</v>
       </c>
       <c r="L3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0036</v>
+        <v>0.0041</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.165</v>
+        <v>2.166</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0399</v>
+        <v>0.0404</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0896</v>
+        <v>0.0901</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0979</v>
+        <v>0.0984</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1311</v>
+        <v>0.1316</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>739.2</v>
+        <v>737</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0028</v>
+        <v>-0.0001</v>
       </c>
       <c r="L4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0028</v>
+        <v>-0.0001</v>
       </c>
       <c r="N4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="O4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="P4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>0.672</v>
+        <v>0.67</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0467</v>
+        <v>0.0436</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0857</v>
+        <v>-0.0884</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1775</v>
+        <v>-0.1799</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0679</v>
+        <v>-0.0707</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994</v>
+        <v>993.8</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.0006</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.0025</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.0025</v>
+      </c>
+      <c r="N5" s="1">
         <v>2.7</v>
       </c>
-      <c r="K5" s="2">
-        <v>0.0027</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="O5" s="1">
         <v>2.7</v>
       </c>
-      <c r="M5" s="2">
-        <v>0.0027</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1.7</v>
-      </c>
       <c r="P5" s="1">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0008</v>
+        <v>0.0006</v>
       </c>
       <c r="U5" s="5">
-        <v>4.97</v>
+        <v>4.969</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0707</v>
+        <v>0.0704</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0523</v>
+        <v>0.0521</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0706</v>
+        <v>0.0703</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3218</v>
+        <v>0.3215</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>985.8</v>
+        <v>986.4</v>
       </c>
       <c r="D6" s="1">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0086</v>
+        <v>0.0092</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="L6" s="1">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="N6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="O6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="P6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0086</v>
+        <v>0.0092</v>
       </c>
       <c r="U6" s="5">
-        <v>9.858</v>
+        <v>9.864</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0115</v>
+        <v>-0.0109</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0837</v>
+        <v>-0.0831</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0879</v>
+        <v>0.0885</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.309</v>
+        <v>0.3098</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.8</v>
+        <v>789.2</v>
       </c>
       <c r="D8" s="1">
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0018</v>
+        <v>-0.0003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0052</v>
+        <v>0.0032</v>
       </c>
       <c r="L8" s="1">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0052</v>
+        <v>0.0032</v>
       </c>
       <c r="N8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="O8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="P8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0018</v>
+        <v>-0.0003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.954</v>
+        <v>3.946</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1504</v>
+        <v>0.1481</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.208</v>
+        <v>0.2056</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2701</v>
+        <v>0.2676</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9929</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="9">
@@ -1113,10 +1113,10 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20246.8</v>
+        <v>20245.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-100.8</v>
+        <v>-102.2</v>
       </c>
       <c r="E9" s="2">
         <v>-0.005</v>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-130.84</v>
+        <v>-132.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="L9" s="1">
-        <v>-130.84</v>
+        <v>-132.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="N9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6772</v>
+        <v>0.6773</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1167,25 +1167,25 @@
         <v>-0.005</v>
       </c>
       <c r="U9" s="5">
-        <v>14.462</v>
+        <v>14.461</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="X9" s="2">
         <v>0.0344</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0097</v>
+        <v>-0.0098</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0599</v>
+        <v>0.0598</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2109</v>
+        <v>0.2108</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>665.6</v>
+        <v>666</v>
       </c>
       <c r="D10" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0006</v>
+        <v>0.0012</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.5</v>
+        <v>-6.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0091</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.5</v>
+        <v>-6.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0091</v>
       </c>
       <c r="N10" s="1">
         <v>-6.1</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0006</v>
+        <v>0.0012</v>
       </c>
       <c r="U10" s="5">
-        <v>1.664</v>
+        <v>1.665</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0096</v>
+        <v>0.009</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0303</v>
+        <v>0.0309</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.286</v>
+        <v>0.2867</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3673</v>
+        <v>0.3681</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3031</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>874.8</v>
+        <v>872</v>
       </c>
       <c r="D11" s="1">
-        <v>15.2</v>
+        <v>12.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0177</v>
+        <v>0.0144</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0166</v>
+        <v>0.0134</v>
       </c>
       <c r="L11" s="1">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0166</v>
+        <v>0.0134</v>
       </c>
       <c r="N11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="O11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="P11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0177</v>
+        <v>0.0144</v>
       </c>
       <c r="U11" s="5">
-        <v>2.187</v>
+        <v>2.18</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.071</v>
+        <v>0.0676</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0379</v>
+        <v>0.0346</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.207</v>
+        <v>0.2031</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3223</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29890.8</v>
+        <v>29883.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-73.8</v>
+        <v>-81.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0025</v>
+        <v>-0.0027</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-100.99</v>
+        <v>-108.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0034</v>
+        <v>-0.0036</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708.6</v>
+        <v>708</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0034</v>
+        <v>-0.0042</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0035</v>
+        <v>-0.0044</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0035</v>
+        <v>-0.0044</v>
       </c>
       <c r="N2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="O2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0034</v>
+        <v>-0.0042</v>
       </c>
       <c r="U2" s="5">
-        <v>3.543</v>
+        <v>3.54</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0037</v>
+        <v>0.0045</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1069</v>
+        <v>0.1059</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0727</v>
+        <v>0.0718</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1753</v>
+        <v>0.1743</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4719</v>
+        <v>0.4707</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866.4</v>
+        <v>866</v>
       </c>
       <c r="D3" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0041</v>
+        <v>0.0036</v>
       </c>
       <c r="L3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0041</v>
+        <v>0.0036</v>
       </c>
       <c r="N3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" s="2">
         <v>0.029</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="U3" s="5">
-        <v>2.166</v>
+        <v>2.165</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0404</v>
+        <v>0.0399</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0901</v>
+        <v>0.0896</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0984</v>
+        <v>0.0979</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1316</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>737</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0001</v>
+        <v>0.0028</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0001</v>
+        <v>0.0028</v>
       </c>
       <c r="N4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.67</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0436</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0884</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1799</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0707</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>993.8</v>
+        <v>994</v>
       </c>
       <c r="D5" s="1">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0006</v>
+        <v>0.0008</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="L5" s="1">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="N5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0006</v>
+        <v>0.0008</v>
       </c>
       <c r="U5" s="5">
-        <v>4.969</v>
+        <v>4.97</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0704</v>
+        <v>0.0707</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0521</v>
+        <v>0.0523</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0703</v>
+        <v>0.0706</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3215</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.4</v>
+        <v>985.9</v>
       </c>
       <c r="D6" s="1">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0092</v>
+        <v>0.0087</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="2">
-        <v>0.013</v>
+        <v>0.0125</v>
       </c>
       <c r="L6" s="1">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="M6" s="2">
-        <v>0.013</v>
+        <v>0.0125</v>
       </c>
       <c r="N6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="P6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0092</v>
+        <v>0.0087</v>
       </c>
       <c r="U6" s="5">
-        <v>9.864</v>
+        <v>9.859</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0109</v>
+        <v>-0.0114</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0831</v>
+        <v>-0.0836</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0885</v>
+        <v>0.088</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3098</v>
+        <v>0.3091</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.101</v>
+        <v>0.1009</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>789.2</v>
+        <v>790.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0032</v>
+        <v>0.0047</v>
       </c>
       <c r="L8" s="1">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0032</v>
+        <v>0.0047</v>
       </c>
       <c r="N8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="O8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="P8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="U8" s="5">
-        <v>3.946</v>
+        <v>3.952</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1481</v>
+        <v>0.1499</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2056</v>
+        <v>0.2074</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2676</v>
+        <v>0.2695</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9889</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20245.4</v>
+        <v>20255.2</v>
       </c>
       <c r="D9" s="1">
-        <v>-102.2</v>
+        <v>-92.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.005</v>
+        <v>-0.0045</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-132.24</v>
+        <v>-122.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0065</v>
+        <v>-0.006</v>
       </c>
       <c r="L9" s="1">
-        <v>-132.24</v>
+        <v>-122.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0065</v>
+        <v>-0.006</v>
       </c>
       <c r="N9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6773</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.005</v>
+        <v>-0.0045</v>
       </c>
       <c r="U9" s="5">
-        <v>14.461</v>
+        <v>14.468</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0065</v>
+        <v>0.006</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0344</v>
+        <v>0.0349</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0098</v>
+        <v>-0.0093</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0598</v>
+        <v>0.0604</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2108</v>
+        <v>0.2114</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>666</v>
+        <v>667.6</v>
       </c>
       <c r="D10" s="1">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0012</v>
+        <v>0.0036</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.1</v>
+        <v>-4.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0067</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.1</v>
+        <v>-4.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0067</v>
       </c>
       <c r="N10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0223</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0012</v>
+        <v>0.0036</v>
       </c>
       <c r="U10" s="5">
-        <v>1.665</v>
+        <v>1.669</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.009</v>
+        <v>0.0066</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0309</v>
+        <v>0.0334</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2867</v>
+        <v>0.2898</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3681</v>
+        <v>0.3714</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3039</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872</v>
+        <v>872.8</v>
       </c>
       <c r="D11" s="1">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0144</v>
+        <v>0.0154</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0134</v>
+        <v>0.0143</v>
       </c>
       <c r="L11" s="1">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0134</v>
+        <v>0.0143</v>
       </c>
       <c r="N11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="O11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="P11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0292</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0144</v>
+        <v>0.0154</v>
       </c>
       <c r="U11" s="5">
-        <v>2.18</v>
+        <v>2.182</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0676</v>
+        <v>0.0686</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0346</v>
+        <v>0.0356</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2031</v>
+        <v>0.2042</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.318</v>
+        <v>0.3193</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29883.4</v>
+        <v>29897.7</v>
       </c>
       <c r="D12" s="1">
-        <v>-81.2</v>
+        <v>-66.9</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0027</v>
+        <v>-0.0022</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-108.39</v>
+        <v>-94.09</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0036</v>
+        <v>-0.0031</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="O12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708</v>
+        <v>709.2</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0042</v>
+        <v>-0.0025</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0044</v>
+        <v>-0.0027</v>
       </c>
       <c r="L2" s="1">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0044</v>
+        <v>-0.0027</v>
       </c>
       <c r="N2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0042</v>
+        <v>-0.0025</v>
       </c>
       <c r="U2" s="5">
-        <v>3.54</v>
+        <v>3.546</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0045</v>
+        <v>0.0028</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1059</v>
+        <v>0.1078</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0718</v>
+        <v>0.0736</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1743</v>
+        <v>0.1763</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4707</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866</v>
+        <v>864.4</v>
       </c>
       <c r="D3" s="1">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0005</v>
+        <v>-0.0014</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0036</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" s="1">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0036</v>
+        <v>0.0017</v>
       </c>
       <c r="N3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.029</v>
+        <v>0.0289</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0005</v>
+        <v>-0.0014</v>
       </c>
       <c r="U3" s="5">
-        <v>2.165</v>
+        <v>2.161</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0399</v>
+        <v>0.038</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0896</v>
+        <v>0.0876</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0979</v>
+        <v>0.0959</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1311</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>739.2</v>
+        <v>740.3</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.0043</v>
+      </c>
+      <c r="L4" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.0043</v>
+      </c>
+      <c r="N4" s="1">
         <v>2.1</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.0028</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="O4" s="1">
         <v>2.1</v>
       </c>
-      <c r="M4" s="2">
-        <v>0.0028</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
       <c r="P4" s="1">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="U4" s="5">
-        <v>0.672</v>
+        <v>0.673</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0467</v>
+        <v>0.0483</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0857</v>
+        <v>-0.0843</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1775</v>
+        <v>-0.1762</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0679</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994</v>
+        <v>995.6</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.0024</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0027</v>
+        <v>0.0043</v>
       </c>
       <c r="L5" s="1">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0027</v>
+        <v>0.0043</v>
       </c>
       <c r="N5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0332</v>
+        <v>0.0333</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0008</v>
+        <v>0.0024</v>
       </c>
       <c r="U5" s="5">
-        <v>4.97</v>
+        <v>4.978</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0707</v>
+        <v>0.0724</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0523</v>
+        <v>0.054</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0706</v>
+        <v>0.0723</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3218</v>
+        <v>0.3239</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>985.9</v>
+        <v>986.1</v>
       </c>
       <c r="D6" s="1">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0087</v>
+        <v>0.0089</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0125</v>
+        <v>0.0127</v>
       </c>
       <c r="L6" s="1">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0125</v>
+        <v>0.0127</v>
       </c>
       <c r="N6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="P6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0087</v>
+        <v>0.0089</v>
       </c>
       <c r="U6" s="5">
-        <v>9.859</v>
+        <v>9.861</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0114</v>
+        <v>-0.0112</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0836</v>
+        <v>-0.0834</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.088</v>
+        <v>0.0882</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3091</v>
+        <v>0.3094</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.4</v>
+        <v>791.6</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0013</v>
+        <v>0.0028</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0047</v>
+        <v>0.0062</v>
       </c>
       <c r="L8" s="1">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0047</v>
+        <v>0.0062</v>
       </c>
       <c r="N8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="O8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="P8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0265</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0013</v>
+        <v>0.0028</v>
       </c>
       <c r="U8" s="5">
-        <v>3.952</v>
+        <v>3.958</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1499</v>
+        <v>0.1516</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2074</v>
+        <v>0.2093</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2695</v>
+        <v>0.2714</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9919</v>
+        <v>0.9949</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20255.2</v>
+        <v>20267.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-92.4</v>
+        <v>-79.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0045</v>
+        <v>-0.0039</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-122.44</v>
+        <v>-109.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.006</v>
+        <v>-0.0054</v>
       </c>
       <c r="L9" s="1">
-        <v>-122.44</v>
+        <v>-109.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.006</v>
+        <v>-0.0054</v>
       </c>
       <c r="N9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="O9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6773</v>
+        <v>0.6774</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0045</v>
+        <v>-0.0039</v>
       </c>
       <c r="U9" s="5">
-        <v>14.468</v>
+        <v>14.477</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.006</v>
+        <v>0.0054</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0349</v>
+        <v>0.0355</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0093</v>
+        <v>-0.0087</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0604</v>
+        <v>0.061</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2114</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>667.6</v>
+        <v>666</v>
       </c>
       <c r="D10" s="1">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0036</v>
+        <v>0.0012</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0067</v>
+        <v>-0.0091</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0067</v>
+        <v>-0.0091</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0223</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0036</v>
+        <v>0.0012</v>
       </c>
       <c r="U10" s="5">
-        <v>1.669</v>
+        <v>1.665</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0066</v>
+        <v>0.009</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0334</v>
+        <v>0.0309</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2898</v>
+        <v>0.2867</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3714</v>
+        <v>0.3681</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.307</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>0.0143</v>
       </c>
       <c r="N11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="O11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="P11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0292</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29897.7</v>
+        <v>29912.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-66.9</v>
+        <v>-52.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0022</v>
+        <v>-0.0017</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-94.09</v>
+        <v>-79.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0031</v>
+        <v>-0.0026</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="O12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="P12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
@@ -1499,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1538,34 +1538,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B2" t="str">
-        <v>14:02:01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>510300</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>300ETF</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4.956</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-991.3</v>
-      </c>
-      <c r="I2" s="6">
-        <v>991.2</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0.1</v>
+        <v>15000</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1576,31 +1570,25 @@
         <v>2026-05-11</v>
       </c>
       <c r="B3" t="str">
-        <v>14:02:37</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>512100</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>1000ETF</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>3.555</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-711.1</v>
-      </c>
-      <c r="I3" s="6">
-        <v>711</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.1</v>
+        <v>15000</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -1611,13 +1599,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B4" t="str">
-        <v>14:02:50</v>
+        <v>14:02:01</v>
       </c>
       <c r="C4" t="str">
-        <v>159915</v>
+        <v>510300</v>
       </c>
       <c r="D4" t="str">
-        <v>创业板</v>
+        <v>300ETF</v>
       </c>
       <c r="E4" t="str">
         <v>买入</v>
@@ -1626,13 +1614,13 @@
         <v>200</v>
       </c>
       <c r="G4">
-        <v>3.933</v>
+        <v>4.956</v>
       </c>
       <c r="H4">
-        <v>-786.7</v>
+        <v>-991.3</v>
       </c>
       <c r="I4" s="6">
-        <v>786.6</v>
+        <v>991.2</v>
       </c>
       <c r="J4" s="6">
         <v>0.1</v>
@@ -1646,28 +1634,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B5" t="str">
-        <v>14:03:06</v>
+        <v>14:02:37</v>
       </c>
       <c r="C5" t="str">
-        <v>513010</v>
+        <v>512100</v>
       </c>
       <c r="D5" t="str">
-        <v>港股科技</v>
+        <v>1000ETF</v>
       </c>
       <c r="E5" t="str">
         <v>买入</v>
       </c>
       <c r="F5">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>0.67</v>
+        <v>3.555</v>
       </c>
       <c r="H5">
-        <v>-737.1</v>
+        <v>-711.1</v>
       </c>
       <c r="I5" s="6">
-        <v>737</v>
+        <v>711</v>
       </c>
       <c r="J5" s="6">
         <v>0.1</v>
@@ -1681,28 +1669,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B6" t="str">
-        <v>14:03:51</v>
+        <v>14:02:50</v>
       </c>
       <c r="C6" t="str">
-        <v>518880</v>
+        <v>159915</v>
       </c>
       <c r="D6" t="str">
-        <v>黄金ETF</v>
+        <v>创业板</v>
       </c>
       <c r="E6" t="str">
         <v>买入</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G6">
-        <v>9.736</v>
+        <v>3.933</v>
       </c>
       <c r="H6">
-        <v>-973.7</v>
+        <v>-786.7</v>
       </c>
       <c r="I6" s="6">
-        <v>973.6</v>
+        <v>786.6</v>
       </c>
       <c r="J6" s="6">
         <v>0.1</v>
@@ -1716,28 +1704,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B7" t="str">
-        <v>14:04:05</v>
+        <v>14:03:06</v>
       </c>
       <c r="C7" t="str">
-        <v>159981</v>
+        <v>513010</v>
       </c>
       <c r="D7" t="str">
-        <v>能源化工</v>
+        <v>港股科技</v>
       </c>
       <c r="E7" t="str">
         <v>买入</v>
       </c>
       <c r="F7">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>0.67</v>
       </c>
       <c r="H7">
-        <v>-672.1</v>
+        <v>-737.1</v>
       </c>
       <c r="I7" s="6">
-        <v>672</v>
+        <v>737</v>
       </c>
       <c r="J7" s="6">
         <v>0.1</v>
@@ -1751,28 +1739,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B8" t="str">
-        <v>14:04:16</v>
+        <v>14:03:51</v>
       </c>
       <c r="C8" t="str">
-        <v>159985</v>
+        <v>518880</v>
       </c>
       <c r="D8" t="str">
-        <v>豆粕ETF</v>
+        <v>黄金ETF</v>
       </c>
       <c r="E8" t="str">
         <v>买入</v>
       </c>
       <c r="F8">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>2.157</v>
+        <v>9.736</v>
       </c>
       <c r="H8">
-        <v>-862.9</v>
+        <v>-973.7</v>
       </c>
       <c r="I8" s="6">
-        <v>862.8</v>
+        <v>973.6</v>
       </c>
       <c r="J8" s="6">
         <v>0.1</v>
@@ -1786,31 +1774,31 @@
         <v>2026-05-11</v>
       </c>
       <c r="B9" t="str">
-        <v>14:04:34</v>
+        <v>14:04:05</v>
       </c>
       <c r="C9" t="str">
-        <v>511380</v>
+        <v>159981</v>
       </c>
       <c r="D9" t="str">
-        <v>转债ETF</v>
+        <v>能源化工</v>
       </c>
       <c r="E9" t="str">
         <v>买入</v>
       </c>
       <c r="F9">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="G9">
-        <v>14.554</v>
+        <v>1.68</v>
       </c>
       <c r="H9">
-        <v>-20377.64</v>
+        <v>-672.1</v>
       </c>
       <c r="I9" s="6">
-        <v>20375.6</v>
+        <v>672</v>
       </c>
       <c r="J9" s="6">
-        <v>2.04</v>
+        <v>0.1</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1821,31 +1809,31 @@
         <v>2026-05-11</v>
       </c>
       <c r="B10" t="str">
-        <v>14:04:49</v>
+        <v>14:04:16</v>
       </c>
       <c r="C10" t="str">
-        <v>166016</v>
+        <v>159985</v>
       </c>
       <c r="D10" t="str">
-        <v>中欧纯债</v>
+        <v>豆粕ETF</v>
       </c>
       <c r="E10" t="str">
         <v>买入</v>
       </c>
       <c r="F10">
-        <v>2700</v>
+        <v>400</v>
       </c>
       <c r="G10">
-        <v>1.118</v>
+        <v>2.157</v>
       </c>
       <c r="H10">
-        <v>-3018.75</v>
+        <v>-862.9</v>
       </c>
       <c r="I10" s="6">
-        <v>3018.6</v>
+        <v>862.8</v>
       </c>
       <c r="J10" s="6">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1856,40 +1844,110 @@
         <v>2026-05-11</v>
       </c>
       <c r="B11" t="str">
-        <v>14:05:33</v>
+        <v>14:04:34</v>
       </c>
       <c r="C11" t="str">
-        <v>159980</v>
+        <v>511380</v>
       </c>
       <c r="D11" t="str">
-        <v>有色ETF</v>
+        <v>转债ETF</v>
       </c>
       <c r="E11" t="str">
         <v>买入</v>
       </c>
       <c r="F11">
+        <v>1400</v>
+      </c>
+      <c r="G11">
+        <v>14.554</v>
+      </c>
+      <c r="H11">
+        <v>-20377.64</v>
+      </c>
+      <c r="I11" s="6">
+        <v>20375.6</v>
+      </c>
+      <c r="J11" s="6">
+        <v>2.04</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>14:04:49</v>
+      </c>
+      <c r="C12" t="str">
+        <v>166016</v>
+      </c>
+      <c r="D12" t="str">
+        <v>中欧纯债</v>
+      </c>
+      <c r="E12" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F12">
+        <v>2700</v>
+      </c>
+      <c r="G12">
+        <v>1.118</v>
+      </c>
+      <c r="H12">
+        <v>-3018.75</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3018.6</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>14:05:33</v>
+      </c>
+      <c r="C13" t="str">
+        <v>159980</v>
+      </c>
+      <c r="D13" t="str">
+        <v>有色ETF</v>
+      </c>
+      <c r="E13" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F13">
         <v>400</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>2.151</v>
       </c>
-      <c r="H11">
+      <c r="H13">
         <v>-860.5</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I13" s="6">
         <v>860.4</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J13" s="6">
         <v>0.1</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>709.2</v>
+        <v>709.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0025</v>
+        <v>-0.002</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0027</v>
+        <v>-0.0021</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0027</v>
+        <v>-0.0021</v>
       </c>
       <c r="N2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0025</v>
+        <v>-0.002</v>
       </c>
       <c r="U2" s="5">
-        <v>3.546</v>
+        <v>3.548</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0028</v>
+        <v>0.0023</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1078</v>
+        <v>0.1084</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0736</v>
+        <v>0.0742</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1763</v>
+        <v>0.177</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4732</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864.4</v>
+        <v>864</v>
       </c>
       <c r="D3" s="1">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0017</v>
+        <v>0.0013</v>
       </c>
       <c r="L3" s="1">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0017</v>
+        <v>0.0013</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="U3" s="5">
-        <v>2.161</v>
+        <v>2.16</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.038</v>
+        <v>0.0375</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0876</v>
+        <v>0.0871</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0959</v>
+        <v>0.0954</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.129</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>740.3</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="L4" s="1">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="N4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="O4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="P4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.673</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0483</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0843</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1762</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0665</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>995.6</v>
+        <v>995.2</v>
       </c>
       <c r="D5" s="1">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0043</v>
+        <v>0.0039</v>
       </c>
       <c r="L5" s="1">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0043</v>
+        <v>0.0039</v>
       </c>
       <c r="N5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0333</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="U5" s="5">
-        <v>4.978</v>
+        <v>4.976</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0724</v>
+        <v>0.072</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.054</v>
+        <v>0.0536</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0723</v>
+        <v>0.0719</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3239</v>
+        <v>0.3234</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.1</v>
+        <v>986.8</v>
       </c>
       <c r="D6" s="1">
-        <v>8.7</v>
+        <v>9.4</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0089</v>
+        <v>0.0096</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0127</v>
+        <v>0.0135</v>
       </c>
       <c r="L6" s="1">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0127</v>
+        <v>0.0135</v>
       </c>
       <c r="N6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="P6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0089</v>
+        <v>0.0096</v>
       </c>
       <c r="U6" s="5">
-        <v>9.861</v>
+        <v>9.868</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0112</v>
+        <v>-0.0105</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0834</v>
+        <v>-0.0828</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0882</v>
+        <v>0.089</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3094</v>
+        <v>0.3103</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>791.6</v>
+        <v>791.8</v>
       </c>
       <c r="D8" s="1">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0062</v>
+        <v>0.0065</v>
       </c>
       <c r="L8" s="1">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0062</v>
+        <v>0.0065</v>
       </c>
       <c r="N8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0265</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.958</v>
+        <v>3.959</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1516</v>
+        <v>0.1519</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2093</v>
+        <v>0.2096</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2714</v>
+        <v>0.2718</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9949</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20267.8</v>
+        <v>20273.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-79.8</v>
+        <v>-74.2</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0039</v>
+        <v>-0.0036</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-109.84</v>
+        <v>-104.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0054</v>
+        <v>-0.0051</v>
       </c>
       <c r="L9" s="1">
-        <v>-109.84</v>
+        <v>-104.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0054</v>
+        <v>-0.0051</v>
       </c>
       <c r="N9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="O9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="P9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6774</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0039</v>
+        <v>-0.0036</v>
       </c>
       <c r="U9" s="5">
-        <v>14.477</v>
+        <v>14.481</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0355</v>
+        <v>0.0358</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0087</v>
+        <v>-0.0084</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.061</v>
+        <v>0.0613</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2121</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>666</v>
+        <v>664.8</v>
       </c>
       <c r="D10" s="1">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0012</v>
+        <v>-0.0006</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.1</v>
+        <v>-7.3</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.1</v>
+        <v>-7.3</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="N10" s="1">
         <v>-6.1</v>
@@ -1238,7 +1238,7 @@
         <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0223</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0012</v>
+        <v>-0.0006</v>
       </c>
       <c r="U10" s="5">
-        <v>1.665</v>
+        <v>1.662</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.009</v>
+        <v>0.0108</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0309</v>
+        <v>0.0291</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2867</v>
+        <v>0.2844</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3681</v>
+        <v>0.3657</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3039</v>
+        <v>0.3015</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872.8</v>
+        <v>874.8</v>
       </c>
       <c r="D11" s="1">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0154</v>
+        <v>0.0177</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>12.3</v>
+        <v>14.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0143</v>
+        <v>0.0166</v>
       </c>
       <c r="L11" s="1">
-        <v>12.3</v>
+        <v>14.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0143</v>
+        <v>0.0166</v>
       </c>
       <c r="N11" s="1">
         <v>11.5</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0154</v>
+        <v>0.0177</v>
       </c>
       <c r="U11" s="5">
-        <v>2.182</v>
+        <v>2.187</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0686</v>
+        <v>0.071</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0356</v>
+        <v>0.0379</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2042</v>
+        <v>0.207</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3193</v>
+        <v>0.3223</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29912.4</v>
+        <v>29918.2</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.2</v>
+        <v>-46.4</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-79.39</v>
+        <v>-73.59</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0026</v>
+        <v>-0.0025</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>707.2</v>
+        <v>717.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.8</v>
+        <v>9.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0011</v>
+        <v>0.0138</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-3.9</v>
+        <v>6.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0055</v>
+        <v>0.0094</v>
       </c>
       <c r="L2" s="1">
-        <v>-3.9</v>
+        <v>6.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0055</v>
+        <v>0.0094</v>
       </c>
       <c r="N2" s="1">
-        <v>-3.1</v>
+        <v>5.9</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.9</v>
+        <v>5.9</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>3</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0011</v>
+        <v>0.0138</v>
       </c>
       <c r="U2" s="5">
-        <v>3.536</v>
+        <v>3.589</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0057</v>
+        <v/>
       </c>
       <c r="X2" s="2">
-        <v>0.1047</v>
+        <v>0.1212</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.06</v>
+        <v>0.0759</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.18</v>
+        <v>0.1977</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4488</v>
+        <v>0.4705</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>867.6</v>
+        <v>862.8</v>
       </c>
       <c r="D3" s="1">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0054</v>
+        <v>-0.0001</v>
       </c>
       <c r="L3" s="1">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0054</v>
+        <v>-0.0001</v>
       </c>
       <c r="N3" s="1">
-        <v>5.1</v>
+        <v>-0.9</v>
       </c>
       <c r="O3" s="1">
-        <v>4.3</v>
+        <v>-0.9</v>
       </c>
       <c r="P3" s="1">
-        <v>4.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0291</v>
+        <v>0.0289</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.169</v>
+        <v>2.157</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0418</v>
+        <v>0.0361</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0905</v>
+        <v>0.0845</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0982</v>
+        <v>0.0921</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1362</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>728.2</v>
+        <v>734.8</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.4</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0121</v>
+        <v>-0.0031</v>
       </c>
       <c r="L4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0121</v>
+        <v>-0.0031</v>
       </c>
       <c r="N4" s="1">
-        <v>-10</v>
+        <v>-2.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="P4" s="1">
-        <v>-8.9</v>
+        <v>-2.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0244</v>
+        <v>0.0246</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.662</v>
+        <v>0.668</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0121</v>
+        <v>0.003</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0312</v>
+        <v>0.0405</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0881</v>
+        <v>-0.0798</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1937</v>
+        <v>-0.1864</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1054</v>
+        <v>-0.0973</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>991.8</v>
+        <v>997.4</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.8</v>
+        <v>4.8</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0008</v>
+        <v>0.0048</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0005</v>
+        <v>0.0062</v>
       </c>
       <c r="L5" s="1">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0005</v>
+        <v>0.0062</v>
       </c>
       <c r="N5" s="1">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="O5" s="1">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="P5" s="1">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0008</v>
+        <v>0.0048</v>
       </c>
       <c r="U5" s="5">
-        <v>4.959</v>
+        <v>4.987</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0683</v>
+        <v>0.0744</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0491</v>
+        <v>0.055</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0677</v>
+        <v>0.0738</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3039</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>981.1</v>
+        <v>979.9</v>
       </c>
       <c r="D6" s="1">
-        <v>0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0076</v>
+        <v>0.0064</v>
       </c>
       <c r="L6" s="1">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0076</v>
+        <v>0.0064</v>
       </c>
       <c r="N6" s="1">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="O6" s="1">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="P6" s="1">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0328</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="U6" s="5">
-        <v>9.811</v>
+        <v>9.799</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0161</v>
+        <v>-0.0173</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0848</v>
+        <v>-0.086</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0867</v>
+        <v>0.0853</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3301</v>
+        <v>0.3285</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1014</v>
+        <v>0.1012</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>787.2</v>
+        <v>803.2</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.8</v>
+        <v>15.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.001</v>
+        <v>0.0193</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0006</v>
+        <v>0.021</v>
       </c>
       <c r="L8" s="1">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0006</v>
+        <v>0.021</v>
       </c>
       <c r="N8" s="1">
-        <v>0.5</v>
+        <v>15.1</v>
       </c>
       <c r="O8" s="1">
-        <v>0.1</v>
+        <v>15.1</v>
       </c>
       <c r="P8" s="1">
-        <v>0.1</v>
+        <v>15.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0269</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.001</v>
+        <v>0.0193</v>
       </c>
       <c r="U8" s="5">
-        <v>3.936</v>
+        <v>4.016</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1451</v>
+        <v>0.1684</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1859</v>
+        <v>0.21</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2664</v>
+        <v>0.2922</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9322</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20151.6</v>
+        <v>20190.8</v>
       </c>
       <c r="D9" s="1">
-        <v>2.8</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-226.04</v>
+        <v>-186.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0111</v>
+        <v>-0.0092</v>
       </c>
       <c r="L9" s="1">
-        <v>-226.04</v>
+        <v>-186.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0111</v>
+        <v>-0.0092</v>
       </c>
       <c r="N9" s="1">
-        <v>-248.44</v>
+        <v>-186.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-237.24</v>
+        <v>-186.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-237.24</v>
+        <v>-186.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6765</v>
+        <v>0.6763</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="U9" s="5">
-        <v>14.394</v>
+        <v>14.422</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0112</v>
+        <v>0.0092</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0296</v>
+        <v>0.0316</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0207</v>
+        <v>-0.0188</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0579</v>
+        <v>0.06</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1959</v>
+        <v>0.1982</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>662</v>
+        <v>657.2</v>
       </c>
       <c r="D10" s="1">
-        <v>-4.8</v>
+        <v>-9.6</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0072</v>
+        <v>-0.0144</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-10.1</v>
+        <v>-14.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.015</v>
+        <v>-0.0222</v>
       </c>
       <c r="L10" s="1">
-        <v>-10.1</v>
+        <v>-14.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.015</v>
+        <v>-0.0222</v>
       </c>
       <c r="N10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="O10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-10.5</v>
+        <v>-14.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0222</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>3</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0072</v>
+        <v>-0.0144</v>
       </c>
       <c r="U10" s="5">
-        <v>1.655</v>
+        <v>1.643</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0151</v>
+        <v>0.0225</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0248</v>
+        <v>0.0173</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2909</v>
+        <v>0.2816</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3499</v>
+        <v>0.3401</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2721</v>
+        <v>0.2629</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>883.2</v>
+        <v>882.8</v>
       </c>
       <c r="D11" s="1">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.017</v>
+        <v>0.0166</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0264</v>
+        <v>0.0259</v>
       </c>
       <c r="L11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0264</v>
+        <v>0.0259</v>
       </c>
       <c r="N11" s="1">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="O11" s="1">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="P11" s="1">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0296</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.017</v>
+        <v>0.0166</v>
       </c>
       <c r="U11" s="5">
-        <v>2.208</v>
+        <v>2.207</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0813</v>
+        <v>0.0808</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0475</v>
+        <v>0.047</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2125</v>
+        <v>0.212</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3182</v>
+        <v>0.3176</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29781.2</v>
+        <v>29848</v>
       </c>
       <c r="D12" s="1">
-        <v>12.1</v>
+        <v>78.9</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0004</v>
+        <v>0.0026</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-210.59</v>
+        <v>-143.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.007</v>
+        <v>-0.0048</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-233.29</v>
+        <v>-146.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-221.19</v>
+        <v>-146.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-221.19</v>
+        <v>-146.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -565,13 +565,13 @@
         <v>0.0094</v>
       </c>
       <c r="N2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="O2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="P2" s="1">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.024</v>
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>862.8</v>
+        <v>864</v>
       </c>
       <c r="D3" s="1">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0009</v>
+        <v>0.0023</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0001</v>
+        <v>0.0013</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0001</v>
+        <v>0.0013</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.9</v>
+        <v>1.1</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0009</v>
+        <v>0.0023</v>
       </c>
       <c r="U3" s="5">
-        <v>2.157</v>
+        <v>2.16</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0361</v>
+        <v>0.0375</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0845</v>
+        <v>0.086</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0921</v>
+        <v>0.0936</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1299</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>734.8</v>
+        <v>732.6</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-2.3</v>
+        <v>-4.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0031</v>
+        <v>-0.0061</v>
       </c>
       <c r="L4" s="1">
-        <v>-2.3</v>
+        <v>-4.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0031</v>
+        <v>-0.0061</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="O4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="P4" s="1">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0246</v>
+        <v>0.0245</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>0.668</v>
+        <v>0.666</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0405</v>
+        <v>0.0374</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0798</v>
+        <v>-0.0826</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1864</v>
+        <v>-0.1888</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0973</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>997.4</v>
+        <v>999</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0062</v>
+        <v>0.0078</v>
       </c>
       <c r="L5" s="1">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0062</v>
+        <v>0.0078</v>
       </c>
       <c r="N5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="P5" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0334</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="U5" s="5">
-        <v>4.987</v>
+        <v>4.995</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0744</v>
+        <v>0.0761</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.055</v>
+        <v>0.0567</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0738</v>
+        <v>0.0755</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3113</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>979.9</v>
+        <v>982.3</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.7</v>
+        <v>1.7</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0064</v>
+        <v>0.0088</v>
       </c>
       <c r="L6" s="1">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0064</v>
+        <v>0.0088</v>
       </c>
       <c r="N6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="O6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="P6" s="1">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="U6" s="5">
-        <v>9.799</v>
+        <v>9.823</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0173</v>
+        <v>-0.0149</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.086</v>
+        <v>-0.0837</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0853</v>
+        <v>0.088</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3285</v>
+        <v>0.3317</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1012</v>
+        <v>0.1011</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>803.2</v>
+        <v>805</v>
       </c>
       <c r="D8" s="1">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0193</v>
+        <v>0.0216</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>16.5</v>
+        <v>18.3</v>
       </c>
       <c r="K8" s="2">
-        <v>0.021</v>
+        <v>0.0233</v>
       </c>
       <c r="L8" s="1">
-        <v>16.5</v>
+        <v>18.3</v>
       </c>
       <c r="M8" s="2">
-        <v>0.021</v>
+        <v>0.0233</v>
       </c>
       <c r="N8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="O8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" s="1">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0269</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0193</v>
+        <v>0.0216</v>
       </c>
       <c r="U8" s="5">
-        <v>4.016</v>
+        <v>4.025</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1684</v>
+        <v>0.171</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.21</v>
+        <v>0.2127</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2922</v>
+        <v>0.295</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9715</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20190.8</v>
+        <v>20197.8</v>
       </c>
       <c r="D9" s="1">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0092</v>
+        <v>-0.0088</v>
       </c>
       <c r="L9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0092</v>
+        <v>-0.0088</v>
       </c>
       <c r="N9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="O9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-186.84</v>
+        <v>-179.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6763</v>
+        <v>0.6762</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="U9" s="5">
-        <v>14.422</v>
+        <v>14.427</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0092</v>
+        <v>0.0089</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0316</v>
+        <v>0.032</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0188</v>
+        <v>-0.0184</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.06</v>
+        <v>0.0604</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1982</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="10">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>882.8</v>
+        <v>886</v>
       </c>
       <c r="D11" s="1">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0166</v>
+        <v>0.0203</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>22.3</v>
+        <v>25.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0259</v>
+        <v>0.0296</v>
       </c>
       <c r="L11" s="1">
-        <v>22.3</v>
+        <v>25.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0259</v>
+        <v>0.0296</v>
       </c>
       <c r="N11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="O11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="P11" s="1">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0296</v>
+        <v>0.0297</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0166</v>
+        <v>0.0203</v>
       </c>
       <c r="U11" s="5">
-        <v>2.207</v>
+        <v>2.215</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0808</v>
+        <v>0.0847</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.047</v>
+        <v>0.0508</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.212</v>
+        <v>0.2164</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3176</v>
+        <v>0.3224</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29848</v>
+        <v>29863</v>
       </c>
       <c r="D12" s="1">
-        <v>78.9</v>
+        <v>93.9</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0026</v>
+        <v>0.0032</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-143.79</v>
+        <v>-128.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0048</v>
+        <v>-0.0043</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="O12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="P12" s="1">
-        <v>-146.69</v>
+        <v>-133.19</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>717.8</v>
+        <v>719.6</v>
       </c>
       <c r="D2" s="1">
-        <v>9.8</v>
+        <v>11.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0138</v>
+        <v>0.0164</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="K2" s="2">
-        <v>0.0094</v>
+        <v>0.012</v>
       </c>
       <c r="L2" s="1">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="M2" s="2">
-        <v>0.0094</v>
+        <v>0.012</v>
       </c>
       <c r="N2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="P2" s="1">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0241</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,10 +583,10 @@
         <v>3</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0138</v>
+        <v>0.0164</v>
       </c>
       <c r="U2" s="5">
-        <v>3.589</v>
+        <v>3.598</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
@@ -595,16 +595,16 @@
         <v/>
       </c>
       <c r="X2" s="2">
-        <v>0.1212</v>
+        <v>0.124</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0759</v>
+        <v>0.0786</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1977</v>
+        <v>0.2007</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4705</v>
+        <v>0.4742</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864</v>
+        <v>864.4</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0023</v>
+        <v>0.0028</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0013</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0013</v>
+        <v>0.0017</v>
       </c>
       <c r="N3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="P3" s="1">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0289</v>
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0023</v>
+        <v>0.0028</v>
       </c>
       <c r="U3" s="5">
-        <v>2.16</v>
+        <v>2.161</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0375</v>
+        <v>0.038</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.086</v>
+        <v>0.0865</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0936</v>
+        <v>0.0941</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1315</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>732.6</v>
+        <v>734.8</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-4.5</v>
+        <v>-2.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0061</v>
+        <v>-0.0031</v>
       </c>
       <c r="L4" s="1">
-        <v>-4.5</v>
+        <v>-2.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0061</v>
+        <v>-0.0031</v>
       </c>
       <c r="N4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="P4" s="1">
-        <v>-3.4</v>
+        <v>-2.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0245</v>
+        <v>0.0246</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.666</v>
+        <v>0.668</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0374</v>
+        <v>0.0405</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0826</v>
+        <v>-0.0798</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1888</v>
+        <v>-0.1864</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1</v>
+        <v>-0.0973</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>999</v>
+        <v>1003.4</v>
       </c>
       <c r="D5" s="1">
-        <v>6.4</v>
+        <v>10.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0064</v>
+        <v>0.0109</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0078</v>
+        <v>0.0122</v>
       </c>
       <c r="L5" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0078</v>
+        <v>0.0122</v>
       </c>
       <c r="N5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="P5" s="1">
-        <v>6.5</v>
+        <v>12.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0334</v>
+        <v>0.0336</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0064</v>
+        <v>0.0109</v>
       </c>
       <c r="U5" s="5">
-        <v>4.995</v>
+        <v>5.017</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0761</v>
+        <v>0.0808</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0567</v>
+        <v>0.0613</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0755</v>
+        <v>0.0802</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3134</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>982.3</v>
+        <v>980.4</v>
       </c>
       <c r="D6" s="1">
-        <v>1.7</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0017</v>
+        <v>-0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0088</v>
+        <v>0.0069</v>
       </c>
       <c r="L6" s="1">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0088</v>
+        <v>0.0069</v>
       </c>
       <c r="N6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="O6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="P6" s="1">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0328</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0017</v>
+        <v>-0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.823</v>
+        <v>9.804</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0149</v>
+        <v>-0.0168</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0837</v>
+        <v>-0.0855</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.088</v>
+        <v>0.0859</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3317</v>
+        <v>0.3291</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1011</v>
+        <v>0.101</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>805</v>
+        <v>809.6</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0216</v>
+        <v>0.0274</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0233</v>
+        <v>0.0291</v>
       </c>
       <c r="L8" s="1">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0233</v>
+        <v>0.0291</v>
       </c>
       <c r="N8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="O8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="P8" s="1">
-        <v>17.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0269</v>
+        <v>0.0271</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0216</v>
+        <v>0.0274</v>
       </c>
       <c r="U8" s="5">
-        <v>4.025</v>
+        <v>4.048</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.171</v>
+        <v>0.1777</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2127</v>
+        <v>0.2196</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.295</v>
+        <v>0.3024</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9759</v>
+        <v>0.9872</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20197.8</v>
+        <v>20220.2</v>
       </c>
       <c r="D9" s="1">
-        <v>49</v>
+        <v>71.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0024</v>
+        <v>0.0035</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0088</v>
+        <v>-0.0077</v>
       </c>
       <c r="L9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0088</v>
+        <v>-0.0077</v>
       </c>
       <c r="N9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="O9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-179.84</v>
+        <v>-157.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6762</v>
+        <v>0.6761</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>3</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0024</v>
+        <v>0.0035</v>
       </c>
       <c r="U9" s="5">
-        <v>14.427</v>
+        <v>14.443</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0089</v>
+        <v>0.0078</v>
       </c>
       <c r="X9" s="2">
-        <v>0.032</v>
+        <v>0.0331</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0184</v>
+        <v>-0.0173</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0604</v>
+        <v>0.0615</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1986</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>657.2</v>
+        <v>660</v>
       </c>
       <c r="D10" s="1">
-        <v>-9.6</v>
+        <v>-6.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0144</v>
+        <v>-0.0102</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0222</v>
+        <v>-0.018</v>
       </c>
       <c r="L10" s="1">
-        <v>-14.9</v>
+        <v>-12.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0222</v>
+        <v>-0.018</v>
       </c>
       <c r="N10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-14.5</v>
+        <v>-12.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.022</v>
+        <v>0.0221</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>3</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0144</v>
+        <v>-0.0102</v>
       </c>
       <c r="U10" s="5">
-        <v>1.643</v>
+        <v>1.65</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0225</v>
+        <v>0.0182</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0173</v>
+        <v>0.0217</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2816</v>
+        <v>0.287</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3401</v>
+        <v>0.3458</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2629</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>886</v>
+        <v>884.4</v>
       </c>
       <c r="D11" s="1">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0203</v>
+        <v>0.0184</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>25.5</v>
+        <v>23.9</v>
       </c>
       <c r="K11" s="2">
+        <v>0.0278</v>
+      </c>
+      <c r="L11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.0278</v>
+      </c>
+      <c r="N11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="O11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="P11" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0.0296</v>
-      </c>
-      <c r="L11" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0.0296</v>
-      </c>
-      <c r="N11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="P11" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>0.0297</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0203</v>
+        <v>0.0184</v>
       </c>
       <c r="U11" s="5">
-        <v>2.215</v>
+        <v>2.211</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0847</v>
+        <v>0.0828</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0508</v>
+        <v>0.0489</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2164</v>
+        <v>0.2142</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3224</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29863</v>
+        <v>29898.1</v>
       </c>
       <c r="D12" s="1">
-        <v>93.9</v>
+        <v>129</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0032</v>
+        <v>0.0043</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-128.79</v>
+        <v>-93.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0043</v>
+        <v>-0.0031</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-133.19</v>
+        <v>-93.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>713.8</v>
+        <v>705.8</v>
       </c>
       <c r="D2" s="1">
-        <v>-5.8</v>
+        <v>-13.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0081</v>
+        <v>-0.0192</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,16 +553,16 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>2.7</v>
+        <v>-5.3</v>
       </c>
       <c r="K2" s="2">
-        <v>0.0038</v>
+        <v>-0.0075</v>
       </c>
       <c r="L2" s="1">
-        <v>2.7</v>
+        <v>-5.3</v>
       </c>
       <c r="M2" s="2">
-        <v>0.0038</v>
+        <v>-0.0075</v>
       </c>
       <c r="N2" s="1">
         <v>2.3</v>
@@ -574,7 +574,7 @@
         <v>2.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.024</v>
+        <v>0.0239</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>4</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0081</v>
+        <v>-0.0192</v>
       </c>
       <c r="U2" s="5">
-        <v>3.569</v>
+        <v>3.529</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v/>
+        <v>0.0077</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1108</v>
+        <v>0.0983</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0865</v>
+        <v>0.0743</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1748</v>
+        <v>0.1616</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4677</v>
+        <v>0.4512</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866.8</v>
+        <v>857.6</v>
       </c>
       <c r="D3" s="1">
-        <v>2.4</v>
+        <v>-6.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0028</v>
+        <v>-0.0079</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.9</v>
+        <v>-5.3</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0045</v>
+        <v>-0.0061</v>
       </c>
       <c r="L3" s="1">
-        <v>3.9</v>
+        <v>-5.3</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0045</v>
+        <v>-0.0061</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -657,7 +657,7 @@
         <v>3.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0291</v>
+        <v>0.029</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>4</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0028</v>
+        <v>-0.0079</v>
       </c>
       <c r="U3" s="5">
-        <v>2.167</v>
+        <v>2.144</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v/>
+        <v>0.0061</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0183</v>
+        <v>0.0075</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0835</v>
+        <v>0.072</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0944</v>
+        <v>0.0828</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1375</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>743.6</v>
+        <v>733.7</v>
       </c>
       <c r="D4" s="1">
-        <v>8.8</v>
+        <v>-1.1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.012</v>
+        <v>-0.0015</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,16 +719,16 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>6.5</v>
+        <v>-3.4</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0088</v>
+        <v>-0.0046</v>
       </c>
       <c r="L4" s="1">
-        <v>6.5</v>
+        <v>-3.4</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0088</v>
+        <v>-0.0046</v>
       </c>
       <c r="N4" s="1">
         <v>7.6</v>
@@ -740,7 +740,7 @@
         <v>7.6</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.025</v>
+        <v>0.0248</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>4</v>
       </c>
       <c r="T4" s="2">
-        <v>0.012</v>
+        <v>-0.0015</v>
       </c>
       <c r="U4" s="5">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v/>
+        <v>0.0045</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0629</v>
+        <v>0.0487</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.065</v>
+        <v>-0.0775</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1856</v>
+        <v>-0.1964</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0778</v>
+        <v>-0.0901</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>997.8</v>
+        <v>988.2</v>
       </c>
       <c r="D5" s="1">
-        <v>-5.6</v>
+        <v>-15.2</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0056</v>
+        <v>-0.0151</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>6.5</v>
+        <v>-3.1</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0066</v>
+        <v>-0.0031</v>
       </c>
       <c r="L5" s="1">
-        <v>6.5</v>
+        <v>-3.1</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0066</v>
+        <v>-0.0031</v>
       </c>
       <c r="N5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="O5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="P5" s="1">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0335</v>
@@ -832,28 +832,28 @@
         <v>4</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0056</v>
+        <v>-0.0151</v>
       </c>
       <c r="U5" s="5">
-        <v>4.989</v>
+        <v>4.941</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v/>
+        <v>0.0032</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0725</v>
+        <v>0.0622</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0681</v>
+        <v>0.0578</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0637</v>
+        <v>0.0535</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3105</v>
+        <v>0.2979</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>978.2</v>
+        <v>979.5</v>
       </c>
       <c r="D6" s="1">
-        <v>-2.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0022</v>
+        <v>-0.0009</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.006</v>
+      </c>
+      <c r="L6" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.006</v>
+      </c>
+      <c r="N6" s="1">
         <v>4.5</v>
       </c>
-      <c r="K6" s="2">
-        <v>0.0046</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="O6" s="1">
         <v>4.5</v>
       </c>
-      <c r="M6" s="2">
-        <v>0.0046</v>
-      </c>
-      <c r="N6" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="O6" s="1">
-        <v>4.2</v>
-      </c>
       <c r="P6" s="1">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0329</v>
+        <v>0.0332</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,10 +915,10 @@
         <v>4</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0022</v>
+        <v>-0.0009</v>
       </c>
       <c r="U6" s="5">
-        <v>9.782</v>
+        <v>9.795</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0143</v>
+        <v>-0.013</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.075</v>
+        <v>-0.0738</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0662</v>
+        <v>0.0676</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3342</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="7">
@@ -947,37 +947,37 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3018.6</v>
       </c>
       <c r="D7" s="1">
+        <v>-2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="L7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="M7" s="2">
         <v>0</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0008</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0008</v>
       </c>
       <c r="N7" s="1">
         <v>2.55</v>
@@ -989,7 +989,7 @@
         <v>2.55</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1015</v>
+        <v>0.1022</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>4</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.118</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0036</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0081</v>
+        <v>0.0072</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0108</v>
+        <v>0.0099</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>804.6</v>
+        <v>792.2</v>
       </c>
       <c r="D8" s="1">
-        <v>-5</v>
+        <v>-17.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0062</v>
+        <v>-0.0215</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>17.9</v>
+        <v>5.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0228</v>
+        <v>0.007</v>
       </c>
       <c r="L8" s="1">
-        <v>17.9</v>
+        <v>5.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0228</v>
+        <v>0.007</v>
       </c>
       <c r="N8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="O8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" s="1">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.027</v>
+        <v>0.0268</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>4</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0062</v>
+        <v>-0.0215</v>
       </c>
       <c r="U8" s="5">
-        <v>4.023</v>
+        <v>3.961</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.16</v>
+        <v>0.1421</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2321</v>
+        <v>0.2132</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2643</v>
+        <v>0.2449</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9818</v>
+        <v>0.9512</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20106.8</v>
+        <v>19923.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-113.4</v>
+        <v>-296.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0056</v>
+        <v>-0.0147</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,16 +1134,16 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-270.84</v>
+        <v>-454.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0133</v>
+        <v>-0.0223</v>
       </c>
       <c r="L9" s="1">
-        <v>-270.84</v>
+        <v>-454.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0133</v>
+        <v>-0.0223</v>
       </c>
       <c r="N9" s="1">
         <v>-269.44</v>
@@ -1155,7 +1155,7 @@
         <v>-269.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6754</v>
+        <v>0.6747</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>4</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0056</v>
+        <v>-0.0147</v>
       </c>
       <c r="U9" s="5">
-        <v>14.362</v>
+        <v>14.231</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0134</v>
+        <v>0.0228</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0313</v>
+        <v>0.0219</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0175</v>
+        <v>-0.0265</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.045</v>
+        <v>0.0355</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1942</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>652.4</v>
+        <v>650.8</v>
       </c>
       <c r="D10" s="1">
-        <v>-7.6</v>
+        <v>-9.2</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0115</v>
+        <v>-0.0139</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-19.7</v>
+        <v>-21.3</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0293</v>
+        <v>-0.0317</v>
       </c>
       <c r="L10" s="1">
-        <v>-19.7</v>
+        <v>-21.3</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0293</v>
+        <v>-0.0317</v>
       </c>
       <c r="N10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-19.7</v>
+        <v>-20.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0219</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>4</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0115</v>
+        <v>-0.0139</v>
       </c>
       <c r="U10" s="5">
-        <v>1.631</v>
+        <v>1.627</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.03</v>
+        <v>0.0326</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0037</v>
+        <v>0.0012</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2852</v>
+        <v>0.2821</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3292</v>
+        <v>0.326</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2441</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>878.8</v>
+        <v>871.6</v>
       </c>
       <c r="D11" s="1">
-        <v>-5.6</v>
+        <v>-12.8</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0063</v>
+        <v>-0.0145</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>18.3</v>
+        <v>11.1</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0213</v>
+        <v>0.0129</v>
       </c>
       <c r="L11" s="1">
-        <v>18.3</v>
+        <v>11.1</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0213</v>
+        <v>0.0129</v>
       </c>
       <c r="N11" s="1">
         <v>18.7</v>
@@ -1330,10 +1330,10 @@
         <v>4</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0063</v>
+        <v>-0.0145</v>
       </c>
       <c r="U11" s="5">
-        <v>2.197</v>
+        <v>2.179</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0686</v>
+        <v>0.0598</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0707</v>
+        <v>0.0619</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1973</v>
+        <v>0.1875</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3132</v>
+        <v>0.3025</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29764.1</v>
+        <v>29521.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-134</v>
+        <v>-376.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0045</v>
+        <v>-0.0126</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-227.69</v>
+        <v>-470.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0076</v>
+        <v>-0.0157</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="O12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="P12" s="1">
-        <v>-225.49</v>
+        <v>-226.99</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
